--- a/confirmation_forms/023_website_handover_confirmation_form--confirmation_forms.xlsx
+++ b/confirmation_forms/023_website_handover_confirmation_form--confirmation_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -734,8 +734,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
-    <col width="37" customWidth="1" min="2" max="2"/>
-    <col width="37" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -763,12 +763,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_2.1,_'label':_'project_a'}</t>
+          <t>project_a</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 2.1, 'label': 'Project A'}</t>
+          <t>Project A</t>
         </is>
       </c>
     </row>
@@ -780,12 +780,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2.2,_'label':_'project_b'}</t>
+          <t>project_b</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2.2, 'label': 'Project B'}</t>
+          <t>Project B</t>
         </is>
       </c>
     </row>
@@ -797,12 +797,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_2.3,_'label':_'project_c'}</t>
+          <t>project_c</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 2.3, 'label': 'Project C'}</t>
+          <t>Project C</t>
         </is>
       </c>
     </row>
@@ -814,12 +814,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_6.1,_'label':_'ftp'}</t>
+          <t>ftp</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 6.1, 'label': 'FTP'}</t>
+          <t>FTP</t>
         </is>
       </c>
     </row>
@@ -831,12 +831,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_6.2,_'label':_'sftp'}</t>
+          <t>sftp</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 6.2, 'label': 'SFTP'}</t>
+          <t>SFTP</t>
         </is>
       </c>
     </row>
@@ -848,12 +848,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_6.3,_'label':_'webdav'}</t>
+          <t>webdav</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 6.3, 'label': 'WebDAV'}</t>
+          <t>WebDAV</t>
         </is>
       </c>
     </row>
@@ -865,12 +865,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_6.4,_'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 6.4, 'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -882,12 +882,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_7.1,_'label':_'pending'}</t>
+          <t>pending</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 7.1, 'label': 'Pending'}</t>
+          <t>Pending</t>
         </is>
       </c>
     </row>
@@ -899,12 +899,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_7.2,_'label':_'in_progress'}</t>
+          <t>in_progress</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 7.2, 'label': 'In Progress'}</t>
+          <t>In Progress</t>
         </is>
       </c>
     </row>
@@ -916,12 +916,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_7.3,_'label':_'complete'}</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 7.3, 'label': 'Complete'}</t>
+          <t>Complete</t>
         </is>
       </c>
     </row>
@@ -933,12 +933,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_7.4,_'label':_'cancelled'}</t>
+          <t>cancelled</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 7.4, 'label': 'Cancelled'}</t>
+          <t>Cancelled</t>
         </is>
       </c>
     </row>
